--- a/data/trans_orig/P62-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P62-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2007</t>
+          <t>Población según si percibe alguna pensión en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>311880</t>
+          <t>311595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>317692</t>
+          <t>318291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>632240</t>
+          <t>633199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>13934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>18854</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>27006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160462</t>
+          <t>160279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171545</t>
+          <t>171476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>265060</t>
+          <t>265163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>278690</t>
+          <t>278863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>430159</t>
+          <t>431224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>448576</t>
+          <t>448615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>17305</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33261</t>
+          <t>34481</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>11836</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33097</t>
+          <t>32827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59281</t>
+          <t>58367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>35189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52981</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>354642</t>
+          <t>354090</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>372097</t>
+          <t>372558</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>394783</t>
+          <t>395697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>420967</t>
+          <t>421237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36655</t>
+          <t>36870</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55133</t>
+          <t>55531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53441</t>
+          <t>54863</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70383</t>
+          <t>71668</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105306</t>
+          <t>105880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25694</t>
+          <t>25296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44172</t>
+          <t>43957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291287</t>
+          <t>289865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315165</t>
+          <t>313739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>320248</t>
+          <t>319674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355171</t>
+          <t>353886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158358</t>
+          <t>157243</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183640</t>
+          <t>183226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67552</t>
+          <t>66580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97650</t>
+          <t>97352</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>230814</t>
+          <t>229211</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276501</t>
+          <t>275537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36970</t>
+          <t>37384</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62252</t>
+          <t>63367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>241184</t>
+          <t>241482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>271282</t>
+          <t>272254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282943</t>
+          <t>283907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>328630</t>
+          <t>330233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>59,03%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>280030</t>
+          <t>280374</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>288345</t>
+          <t>288356</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>158212</t>
+          <t>160147</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193195</t>
+          <t>193444</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>441335</t>
+          <t>440718</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>483667</t>
+          <t>485195</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9641</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>145268</t>
+          <t>145019</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>180251</t>
+          <t>178316</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144812</t>
+          <t>143284</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>187144</t>
+          <t>187761</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>202260</t>
+          <t>202221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>228556</t>
+          <t>230802</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>263261</t>
+          <t>262729</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>436588</t>
+          <t>434887</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>470422</t>
+          <t>470160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>69573</t>
+          <t>70105</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104278</t>
+          <t>102032</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>69825</t>
+          <t>70087</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103659</t>
+          <t>105360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>704703</t>
+          <t>706023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>777999</t>
+          <t>776905</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>535011</t>
+          <t>538793</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>619576</t>
+          <t>620420</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1262052</t>
+          <t>1264825</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1379693</t>
+          <t>1381379</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>581344</t>
+          <t>582438</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>654640</t>
+          <t>653320</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1726965</t>
+          <t>1726121</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1811530</t>
+          <t>1807748</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2326190</t>
+          <t>2324504</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2443831</t>
+          <t>2441058</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2012</t>
+          <t>Población según si percibe alguna pensión en 2012 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>977</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22756</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>350477</t>
+          <t>350648</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>359144</t>
+          <t>359143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>323080</t>
+          <t>322432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>335884</t>
+          <t>336503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>677893</t>
+          <t>677281</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693684</t>
+          <t>693052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26484</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>17036</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37253</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>30229</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57063</t>
+          <t>56531</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>273856</t>
+          <t>274110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>290459</t>
+          <t>290368</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>290748</t>
+          <t>290767</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311296</t>
+          <t>310965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>571278</t>
+          <t>571810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>597848</t>
+          <t>598112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34895</t>
+          <t>33887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63151</t>
+          <t>61834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28457</t>
+          <t>28330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>54831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70423</t>
+          <t>68134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105840</t>
+          <t>103710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188318</t>
+          <t>189635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>216574</t>
+          <t>217582</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>361216</t>
+          <t>361495</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>387869</t>
+          <t>387996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>561956</t>
+          <t>564086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>597373</t>
+          <t>599662</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61221</t>
+          <t>62173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92975</t>
+          <t>92024</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41398</t>
+          <t>42696</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71904</t>
+          <t>70641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109333</t>
+          <t>111361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151249</t>
+          <t>154183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151893</t>
+          <t>152844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183647</t>
+          <t>182695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>310587</t>
+          <t>311850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>341093</t>
+          <t>339795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>476110</t>
+          <t>473176</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>518026</t>
+          <t>515998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157565</t>
+          <t>158066</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190480</t>
+          <t>192065</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78202</t>
+          <t>78765</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114061</t>
+          <t>114787</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>243664</t>
+          <t>243485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>297715</t>
+          <t>295564</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77515</t>
+          <t>75930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110430</t>
+          <t>109929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>256994</t>
+          <t>256268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>292853</t>
+          <t>292290</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341335</t>
+          <t>343486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395386</t>
+          <t>395565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>301107</t>
+          <t>301275</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>207912</t>
+          <t>206457</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243423</t>
+          <t>242556</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>510005</t>
+          <t>510536</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>550463</t>
+          <t>551072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>104816</t>
+          <t>105683</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140327</t>
+          <t>141782</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104546</t>
+          <t>103937</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145004</t>
+          <t>144473</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>244528</t>
+          <t>244491</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>280565</t>
+          <t>280107</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>313548</t>
+          <t>313613</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>526506</t>
+          <t>525309</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>561995</t>
+          <t>562931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>73350</t>
+          <t>73285</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106333</t>
+          <t>106791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74754</t>
+          <t>73818</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>110243</t>
+          <t>111440</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>822352</t>
+          <t>827419</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>917084</t>
+          <t>915256</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>699546</t>
+          <t>705813</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>792414</t>
+          <t>795939</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1556186</t>
+          <t>1555651</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1691213</t>
+          <t>1682935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1064329</t>
+          <t>1066157</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1159061</t>
+          <t>1153994</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1781124</t>
+          <t>1777599</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1873992</t>
+          <t>1867725</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2863739</t>
+          <t>2872017</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2998766</t>
+          <t>2999301</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2016</t>
+          <t>Población según si percibe alguna pensión en 2016 (tasa de respuesta: 98,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18611</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24379</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>316215</t>
+          <t>316530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325602</t>
+          <t>325939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270163</t>
+          <t>269923</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283030</t>
+          <t>283024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>591396</t>
+          <t>591172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>607133</t>
+          <t>606790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>22039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18937</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>39740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>219770</t>
+          <t>221409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>235123</t>
+          <t>236135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262162</t>
+          <t>263044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277381</t>
+          <t>277091</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>488856</t>
+          <t>488201</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>509004</t>
+          <t>509088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19654</t>
+          <t>20564</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40405</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41305</t>
+          <t>40732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46863</t>
+          <t>45911</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75539</t>
+          <t>74491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167790</t>
+          <t>168287</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>188541</t>
+          <t>187631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301728</t>
+          <t>302301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321591</t>
+          <t>321963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>475688</t>
+          <t>476736</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>504364</t>
+          <t>505316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63895</t>
+          <t>65665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96483</t>
+          <t>97461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36050</t>
+          <t>35695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62199</t>
+          <t>61799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106006</t>
+          <t>107696</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147900</t>
+          <t>148870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180570</t>
+          <t>179592</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213158</t>
+          <t>211388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>331678</t>
+          <t>332078</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357827</t>
+          <t>358182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>523030</t>
+          <t>522060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>564924</t>
+          <t>563234</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182054</t>
+          <t>182557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217670</t>
+          <t>216617</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>93747</t>
+          <t>94548</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133099</t>
+          <t>132172</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>285111</t>
+          <t>284968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>341087</t>
+          <t>339823</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92641</t>
+          <t>93694</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128257</t>
+          <t>127754</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>250201</t>
+          <t>251128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>289553</t>
+          <t>288752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>352523</t>
+          <t>353787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408499</t>
+          <t>408642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>317208</t>
+          <t>316521</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>326296</t>
+          <t>326271</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>215024</t>
+          <t>213709</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>251807</t>
+          <t>252419</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>531299</t>
+          <t>534544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>578362</t>
+          <t>578188</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,98%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116781</t>
+          <t>116169</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153564</t>
+          <t>154879</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118441</t>
+          <t>118615</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165504</t>
+          <t>162259</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>246452</t>
+          <t>246712</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>274597</t>
+          <t>272817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314140</t>
+          <t>313101</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>521564</t>
+          <t>524541</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>564487</t>
+          <t>566298</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>82072</t>
+          <t>83111</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121615</t>
+          <t>123395</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>83819</t>
+          <t>82008</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126742</t>
+          <t>123765</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>858465</t>
+          <t>857980</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>945068</t>
+          <t>945922</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>695881</t>
+          <t>693930</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>792794</t>
+          <t>788550</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1583199</t>
+          <t>1575264</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1710332</t>
+          <t>1701824</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1001248</t>
+          <t>1000394</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1087851</t>
+          <t>1088336</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1665482</t>
+          <t>1669726</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1762395</t>
+          <t>1764346</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2694261</t>
+          <t>2702769</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2821394</t>
+          <t>2829329</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2023</t>
+          <t>Población según si percibe alguna pensión en 2023 (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14056</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19778</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295636</t>
+          <t>298199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212361</t>
+          <t>212252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224918</t>
+          <t>224894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514353</t>
+          <t>516001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531804</t>
+          <t>532375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>16762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>20252</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32278</t>
+          <t>32677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55528</t>
+          <t>55087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68564</t>
+          <t>68565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137681</t>
+          <t>138336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>152333</t>
+          <t>152324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>198159</t>
+          <t>197760</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217930</t>
+          <t>217993</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28134</t>
+          <t>27740</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19421</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35021</t>
+          <t>35377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57639</t>
+          <t>58835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43940</t>
+          <t>44334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59735</t>
+          <t>59467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154652</t>
+          <t>154296</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>170252</t>
+          <t>169909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>204108</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>225699</t>
+          <t>226087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>43199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66501</t>
+          <t>66067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32775</t>
+          <t>32274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51187</t>
+          <t>51085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82110</t>
+          <t>80394</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113478</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69240</t>
+          <t>69674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92993</t>
+          <t>92542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205758</t>
+          <t>205860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>224170</t>
+          <t>224671</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,17 +10877,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>296778</t>
+          <t>296779</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279207</t>
+          <t>280495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310575</t>
+          <t>312292</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>392685</t>
+          <t>392686</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>392685</t>
+          <t>392686</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>392685</t>
+          <t>392686</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155408</t>
+          <t>155990</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183716</t>
+          <t>183832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95537</t>
+          <t>93792</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120348</t>
+          <t>119034</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255838</t>
+          <t>255729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>295432</t>
+          <t>296351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,82%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77050</t>
+          <t>76934</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105358</t>
+          <t>104776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>213727</t>
+          <t>215041</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>238538</t>
+          <t>240283</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>299408</t>
+          <t>298489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>339002</t>
+          <t>339111</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>287367</t>
+          <t>288007</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>308985</t>
+          <t>309281</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>340290</t>
+          <t>340293</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>527377</t>
+          <t>523028</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>664273</t>
+          <t>665922</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>834134</t>
+          <t>839032</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42237</t>
+          <t>41941</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63855</t>
+          <t>63215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61514</t>
+          <t>65863</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248601</t>
+          <t>248598</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105979</t>
+          <t>101081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>275840</t>
+          <t>274191</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>238161</t>
+          <t>237326</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>255654</t>
+          <t>254840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>307203</t>
+          <t>306211</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>331649</t>
+          <t>331261</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>550930</t>
+          <t>550407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>582094</t>
+          <t>581291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,49%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25507</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43000</t>
+          <t>43835</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>91866</t>
+          <t>92254</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116312</t>
+          <t>117304</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>122582</t>
+          <t>123385</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>153746</t>
+          <t>154269</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>757945</t>
+          <t>757511</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>846187</t>
+          <t>850378</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>801281</t>
+          <t>803430</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1350692</t>
+          <t>1297233</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1612998</t>
+          <t>1614534</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2158940</t>
+          <t>2133061</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>634340</t>
+          <t>630149</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>722582</t>
+          <t>723016</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>827411</t>
+          <t>880870</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1376822</t>
+          <t>1374673</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1499690</t>
+          <t>1525569</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2045632</t>
+          <t>2044096</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P62-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P62-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>311595</t>
+          <t>310258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>318291</t>
+          <t>317351</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>633199</t>
+          <t>633241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13934</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>19734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>27341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160279</t>
+          <t>161737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171476</t>
+          <t>171872</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>265163</t>
+          <t>264283</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>278863</t>
+          <t>279112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>431224</t>
+          <t>430889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>448615</t>
+          <t>447793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17305</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34481</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>12294</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30304</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>32333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58367</t>
+          <t>58937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35189</t>
+          <t>35977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>51588</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>354090</t>
+          <t>354423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>372558</t>
+          <t>372100</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>395697</t>
+          <t>395127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>421237</t>
+          <t>421731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36870</t>
+          <t>36164</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55531</t>
+          <t>54551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30989</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54863</t>
+          <t>53561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71668</t>
+          <t>70939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105880</t>
+          <t>103132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25296</t>
+          <t>26276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43957</t>
+          <t>44663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>289865</t>
+          <t>291167</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>313739</t>
+          <t>314750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>319674</t>
+          <t>322422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>353886</t>
+          <t>354615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157243</t>
+          <t>158155</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183226</t>
+          <t>183199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66580</t>
+          <t>66155</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97352</t>
+          <t>97199</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>229211</t>
+          <t>229545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>275537</t>
+          <t>276127</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37384</t>
+          <t>37411</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63367</t>
+          <t>62455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>241482</t>
+          <t>241635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>272254</t>
+          <t>272679</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283907</t>
+          <t>283317</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>330233</t>
+          <t>329899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,97%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>280374</t>
+          <t>280260</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>288356</t>
+          <t>288335</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>160147</t>
+          <t>159336</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193444</t>
+          <t>193912</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>440718</t>
+          <t>442538</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>485195</t>
+          <t>484120</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>9755</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>145019</t>
+          <t>144551</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>178316</t>
+          <t>179127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143284</t>
+          <t>144359</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>187761</t>
+          <t>185941</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>202221</t>
+          <t>201436</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>230802</t>
+          <t>228789</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>262729</t>
+          <t>263211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>434887</t>
+          <t>433249</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>470160</t>
+          <t>469995</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70105</t>
+          <t>69623</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>102032</t>
+          <t>104045</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70087</t>
+          <t>70252</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>105360</t>
+          <t>106998</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>706023</t>
+          <t>704978</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>776905</t>
+          <t>776480</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>538793</t>
+          <t>536304</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>620420</t>
+          <t>621544</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1264825</t>
+          <t>1267016</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1381379</t>
+          <t>1382544</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>582438</t>
+          <t>582863</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>653320</t>
+          <t>654365</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1726121</t>
+          <t>1724997</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1807748</t>
+          <t>1810237</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2324504</t>
+          <t>2323339</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2441058</t>
+          <t>2438867</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>9663</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23368</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>350648</t>
+          <t>350457</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>359143</t>
+          <t>359147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>322432</t>
+          <t>322610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>336503</t>
+          <t>335862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>677281</t>
+          <t>677992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693052</t>
+          <t>693591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17036</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37234</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30229</t>
+          <t>30289</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56531</t>
+          <t>56076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>274110</t>
+          <t>274967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>290368</t>
+          <t>290441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>290767</t>
+          <t>291259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>310965</t>
+          <t>311530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>571810</t>
+          <t>572265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>598112</t>
+          <t>598052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33887</t>
+          <t>33452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61834</t>
+          <t>60757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28330</t>
+          <t>27977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54831</t>
+          <t>54108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68134</t>
+          <t>67640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103710</t>
+          <t>106044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189635</t>
+          <t>190712</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>217582</t>
+          <t>218017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>361495</t>
+          <t>362218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>387996</t>
+          <t>388349</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>564086</t>
+          <t>561752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>599662</t>
+          <t>600156</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62173</t>
+          <t>62417</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92024</t>
+          <t>91821</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42696</t>
+          <t>41724</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70641</t>
+          <t>70396</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111361</t>
+          <t>109578</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154183</t>
+          <t>153936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152844</t>
+          <t>153047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182695</t>
+          <t>182451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>311850</t>
+          <t>312095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>339795</t>
+          <t>340767</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>473176</t>
+          <t>473423</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>515998</t>
+          <t>517781</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158066</t>
+          <t>158224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192065</t>
+          <t>191008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78765</t>
+          <t>78662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114787</t>
+          <t>113602</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>243485</t>
+          <t>243541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>295564</t>
+          <t>297642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75930</t>
+          <t>76987</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109929</t>
+          <t>109771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>256268</t>
+          <t>257453</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>292290</t>
+          <t>292393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>343486</t>
+          <t>341408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395565</t>
+          <t>395509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>301275</t>
+          <t>301119</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206457</t>
+          <t>207708</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>242556</t>
+          <t>242909</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>510536</t>
+          <t>509435</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>551072</t>
+          <t>550793</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105683</t>
+          <t>105330</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>141782</t>
+          <t>140531</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>103937</t>
+          <t>104216</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144473</t>
+          <t>145574</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>244491</t>
+          <t>244977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>280107</t>
+          <t>280202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>313613</t>
+          <t>314692</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>525309</t>
+          <t>527271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>562931</t>
+          <t>562333</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>73285</t>
+          <t>72206</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106791</t>
+          <t>106696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>73818</t>
+          <t>74416</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>111440</t>
+          <t>109478</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>827419</t>
+          <t>827071</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>915256</t>
+          <t>916749</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>705813</t>
+          <t>700539</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>795939</t>
+          <t>796120</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1555651</t>
+          <t>1557149</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1682935</t>
+          <t>1690707</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1066157</t>
+          <t>1064664</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1153994</t>
+          <t>1154342</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1777599</t>
+          <t>1777418</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1867725</t>
+          <t>1872999</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2872017</t>
+          <t>2864245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2999301</t>
+          <t>2997803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>24538</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>316530</t>
+          <t>315769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325939</t>
+          <t>325940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269923</t>
+          <t>269613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283024</t>
+          <t>282985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>591172</t>
+          <t>591237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>606790</t>
+          <t>606919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22039</t>
+          <t>23934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>17977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39740</t>
+          <t>39846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>221409</t>
+          <t>219514</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>236135</t>
+          <t>235054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263044</t>
+          <t>264256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277091</t>
+          <t>277774</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>488201</t>
+          <t>488095</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>509088</t>
+          <t>509964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>20667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>40515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40732</t>
+          <t>41484</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>45014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74491</t>
+          <t>74430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168287</t>
+          <t>167680</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>187631</t>
+          <t>187528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>302301</t>
+          <t>301549</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321963</t>
+          <t>321782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>476736</t>
+          <t>476797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>505316</t>
+          <t>506213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65665</t>
+          <t>64512</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97461</t>
+          <t>95682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35695</t>
+          <t>36759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61799</t>
+          <t>62684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107696</t>
+          <t>107781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148870</t>
+          <t>149894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179592</t>
+          <t>181371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211388</t>
+          <t>212541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>332078</t>
+          <t>331193</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358182</t>
+          <t>357118</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>522060</t>
+          <t>521036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>563234</t>
+          <t>563149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,94%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182557</t>
+          <t>183083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>216617</t>
+          <t>217065</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94548</t>
+          <t>94653</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132172</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>284968</t>
+          <t>286447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>339823</t>
+          <t>339363</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93694</t>
+          <t>93246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127754</t>
+          <t>127228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>251128</t>
+          <t>250582</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>288752</t>
+          <t>288647</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>353787</t>
+          <t>354247</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408642</t>
+          <t>407163</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,7%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>316521</t>
+          <t>317404</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>326271</t>
+          <t>326293</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>213709</t>
+          <t>214145</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>252419</t>
+          <t>252318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>534544</t>
+          <t>534954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>578188</t>
+          <t>577084</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,82%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116169</t>
+          <t>116270</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>154879</t>
+          <t>154443</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118615</t>
+          <t>119719</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>161849</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>246712</t>
+          <t>245963</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>272817</t>
+          <t>275446</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>313101</t>
+          <t>313860</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>524541</t>
+          <t>523174</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>566298</t>
+          <t>564591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83111</t>
+          <t>82352</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>123395</t>
+          <t>120766</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>82008</t>
+          <t>83715</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>123765</t>
+          <t>125132</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>857980</t>
+          <t>855290</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>945922</t>
+          <t>942040</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>693930</t>
+          <t>693138</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>788550</t>
+          <t>788114</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1575264</t>
+          <t>1582330</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1701824</t>
+          <t>1705488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1000394</t>
+          <t>1004276</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1088336</t>
+          <t>1091026</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1669726</t>
+          <t>1670162</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1764346</t>
+          <t>1765138</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2702769</t>
+          <t>2699105</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2829329</t>
+          <t>2822263</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>16043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>18752</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>305725</t>
+          <t>299375</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>298199</t>
+          <t>292302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307715</t>
+          <t>301128</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>220921</t>
+          <t>260031</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212252</t>
+          <t>249372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224894</t>
+          <t>263946</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>526645</t>
+          <t>559405</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516001</t>
+          <t>547791</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>532375</t>
+          <t>564803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>307715</t>
+          <t>301128</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>307715</t>
+          <t>301128</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>307715</t>
+          <t>301128</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>226417</t>
+          <t>265415</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>226417</t>
+          <t>265415</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>226417</t>
+          <t>265415</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>534131</t>
+          <t>566543</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>534131</t>
+          <t>566543</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>534131</t>
+          <t>566543</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20178</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32677</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>63726</t>
+          <t>71415</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55087</t>
+          <t>63116</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68565</t>
+          <t>76094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>146533</t>
+          <t>168732</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>138336</t>
+          <t>159216</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>152324</t>
+          <t>175134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>210259</t>
+          <t>240147</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197760</t>
+          <t>227700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217993</t>
+          <t>248100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71849</t>
+          <t>79777</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71849</t>
+          <t>79777</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71849</t>
+          <t>79777</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>158588</t>
+          <t>181878</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>158588</t>
+          <t>181878</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>158588</t>
+          <t>181878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>230437</t>
+          <t>261655</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>230437</t>
+          <t>261655</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>230437</t>
+          <t>261655</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>13543</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26592</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19764</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35377</t>
+          <t>38069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46463</t>
+          <t>49578</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35660</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58835</t>
+          <t>62246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>59345</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44334</t>
+          <t>49718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59467</t>
+          <t>66637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>163081</t>
+          <t>194156</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154296</t>
+          <t>184830</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>169909</t>
+          <t>201916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>215284</t>
+          <t>253501</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>240833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>226087</t>
+          <t>264464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72074</t>
+          <t>80180</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72074</t>
+          <t>80180</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72074</t>
+          <t>80180</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>189673</t>
+          <t>222899</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189673</t>
+          <t>222899</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>189673</t>
+          <t>222899</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>261747</t>
+          <t>303079</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>261747</t>
+          <t>303079</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>261747</t>
+          <t>303079</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54596</t>
+          <t>60716</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43199</t>
+          <t>48215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66067</t>
+          <t>74039</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41311</t>
+          <t>46132</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32274</t>
+          <t>36952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51085</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>95907</t>
+          <t>106848</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80394</t>
+          <t>91010</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112191</t>
+          <t>124957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>81145</t>
+          <t>89483</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69674</t>
+          <t>76160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92542</t>
+          <t>101984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>215634</t>
+          <t>232745</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205860</t>
+          <t>221780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>224671</t>
+          <t>241925</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>296779</t>
+          <t>322228</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280495</t>
+          <t>304119</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312292</t>
+          <t>338066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>135741</t>
+          <t>150199</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>135741</t>
+          <t>150199</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135741</t>
+          <t>150199</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>256945</t>
+          <t>278877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>256945</t>
+          <t>278877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>256945</t>
+          <t>278877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>392686</t>
+          <t>429076</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>392686</t>
+          <t>429076</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>392686</t>
+          <t>429076</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>170209</t>
+          <t>179528</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155990</t>
+          <t>163647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183832</t>
+          <t>194090</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>106361</t>
+          <t>117879</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>93792</t>
+          <t>105499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119034</t>
+          <t>135273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>276570</t>
+          <t>297408</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255729</t>
+          <t>275677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>296351</t>
+          <t>318797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>90557</t>
+          <t>98797</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76934</t>
+          <t>84235</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104776</t>
+          <t>114678</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>227714</t>
+          <t>253423</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>215041</t>
+          <t>236029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>240283</t>
+          <t>265803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>318270</t>
+          <t>352219</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>298489</t>
+          <t>330830</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>339111</t>
+          <t>373950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>260766</t>
+          <t>278325</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>260766</t>
+          <t>278325</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>260766</t>
+          <t>278325</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>334075</t>
+          <t>371302</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>334075</t>
+          <t>371302</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>334075</t>
+          <t>371302</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>594840</t>
+          <t>649627</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>594840</t>
+          <t>649627</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>594840</t>
+          <t>649627</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>299517</t>
+          <t>331580</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>288007</t>
+          <t>319495</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>309281</t>
+          <t>341891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>431816</t>
+          <t>249490</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>340293</t>
+          <t>234875</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>523028</t>
+          <t>263979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>731333</t>
+          <t>581071</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>665922</t>
+          <t>561932</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>839032</t>
+          <t>601679</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>51705</t>
+          <t>56333</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41941</t>
+          <t>46022</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63215</t>
+          <t>68418</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>157075</t>
+          <t>168028</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65863</t>
+          <t>153539</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248598</t>
+          <t>182643</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>208780</t>
+          <t>224360</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101081</t>
+          <t>203752</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>274191</t>
+          <t>243499</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>351222</t>
+          <t>387913</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>351222</t>
+          <t>387913</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>351222</t>
+          <t>387913</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>588891</t>
+          <t>417518</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>588891</t>
+          <t>417518</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>588891</t>
+          <t>417518</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>940113</t>
+          <t>805431</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>940113</t>
+          <t>805431</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>940113</t>
+          <t>805431</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>247165</t>
+          <t>271675</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>237326</t>
+          <t>262018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>254840</t>
+          <t>280009</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>319332</t>
+          <t>349990</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>306211</t>
+          <t>336130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>331261</t>
+          <t>361871</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>566497</t>
+          <t>621665</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>550407</t>
+          <t>605355</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>581291</t>
+          <t>637501</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>36707</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>28373</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43835</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>104183</t>
+          <t>112179</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>92254</t>
+          <t>100298</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>117304</t>
+          <t>126039</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>138179</t>
+          <t>148886</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>123385</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>154269</t>
+          <t>165196</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281161</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281161</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281161</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423515</t>
+          <t>462169</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423515</t>
+          <t>462169</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>423515</t>
+          <t>462169</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>704676</t>
+          <t>770551</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>704676</t>
+          <t>770551</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>704676</t>
+          <t>770551</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>801470</t>
+          <t>874450</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>757511</t>
+          <t>827195</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>850378</t>
+          <t>916420</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>942962</t>
+          <t>810764</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>803430</t>
+          <t>772622</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1297233</t>
+          <t>847928</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1744432</t>
+          <t>1685213</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1614534</t>
+          <t>1622520</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2133061</t>
+          <t>1743348</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>46,05%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>679057</t>
+          <t>711454</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>630149</t>
+          <t>669484</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>723016</t>
+          <t>758709</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1235141</t>
+          <t>1389294</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>880870</t>
+          <t>1352130</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1374673</t>
+          <t>1427436</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1914198</t>
+          <t>2100749</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1525569</t>
+          <t>2042614</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2044096</t>
+          <t>2163442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1480527</t>
+          <t>1585904</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1480527</t>
+          <t>1585904</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1480527</t>
+          <t>1585904</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2178103</t>
+          <t>2200058</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2178103</t>
+          <t>2200058</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2178103</t>
+          <t>2200058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3658630</t>
+          <t>3785962</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3658630</t>
+          <t>3785962</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3658630</t>
+          <t>3785962</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
